--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260703.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260703.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>13.23%</t>
+          <t>13.21%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.08%</t>
+          <t>12.17%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>658,330,000</t>
+          <t>876,177,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>11.66%</t>
+          <t>11.56%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>876,177,000</t>
+          <t>658,950,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>11.60%</t>
+          <t>11.52%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.10%</t>
+          <t>7.25%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>4.28%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>4.12%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.73%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.60%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>22,310,000</t>
+          <t>22,400,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.28%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1232,51 +1232,51 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>34,120,000</t>
+          <t>26,819,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>14,250,000</t>
+          <t>34,120,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>26,819,000</t>
+          <t>38,623,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,39 +1371,39 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>38,623,000</t>
+          <t>14,250,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,39 +1415,39 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,990,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>7,990,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>29,006,000</t>
+          <t>20,520,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,22 +1481,22 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>20,520,000</t>
+          <t>29,006,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1575,17 +1575,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>B20165</t>
+          <t>B20166</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>P10亞泥1</t>
+          <t>P12亞泥1</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>150,000,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr"/>
@@ -1593,17 +1593,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>B20166</t>
+          <t>B20247</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>P12亞泥1</t>
+          <t>P09台泥1B</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>150,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
@@ -1611,17 +1611,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>B20247</t>
+          <t>B20258</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>P09台泥1B</t>
+          <t>P14台泥1A</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr"/>
@@ -1629,17 +1629,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>B20258</t>
+          <t>B401DV</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>P14台泥1A</t>
+          <t>P14南亞2A</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>100,028,603</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr"/>
@@ -1647,12 +1647,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>B30453</t>
+          <t>B402BF</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>P11統一1A</t>
+          <t>P09台塑1B</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1665,17 +1665,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>B401DV</t>
+          <t>B402BJ</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>P14南亞2A</t>
+          <t>P10台塑1B</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>100,028,603</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1683,17 +1683,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>B402BF</t>
+          <t>B402BR</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>P09台塑1B</t>
+          <t>P14台塑1</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>800,120,051</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1701,12 +1701,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>B402BJ</t>
+          <t>B50181</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>P10台塑1B</t>
+          <t>P13遠東新1</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -1719,17 +1719,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>B402BK</t>
+          <t>B50187</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>P12台塑1A</t>
+          <t>P13遠東新7</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1737,17 +1737,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>B402BR</t>
+          <t>B50191</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>P14台塑1</t>
+          <t>P14遠東新2</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>800,120,051</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
@@ -1755,17 +1755,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>B50181</t>
+          <t>B618BR</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>P13遠東新1</t>
+          <t>P09台積2B</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr"/>
@@ -1773,17 +1773,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>B50187</t>
+          <t>B618BS</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>P13遠東新7</t>
+          <t>P09台積2C</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>150,000,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr"/>
@@ -1791,12 +1791,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>B50191</t>
+          <t>B618BV</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>P14遠東新2</t>
+          <t>P09台積3C</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -1809,12 +1809,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>B618BR</t>
+          <t>B618DK</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>P09台積2B</t>
+          <t>P12台積3A</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -1827,17 +1827,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>B618BS</t>
+          <t>B62942</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>P09台積2C</t>
+          <t>P11佳世達1</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>150,000,000</t>
+          <t>27,100,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr"/>
@@ -1845,17 +1845,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>B618BV</t>
+          <t>B638BJ</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>P09台積3C</t>
+          <t>P14聯電1A</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>250,000,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
@@ -1863,17 +1863,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>B618DK</t>
+          <t>B644C6</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>P12台積3A</t>
+          <t>P10鴻海2B</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>160,000,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr"/>
@@ -1881,17 +1881,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>B618E6</t>
+          <t>B644D6</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>P14台積5A</t>
+          <t>P13鴻海1B</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>90,000,000</t>
+          <t>170,000,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr"/>
@@ -1899,17 +1899,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>B62942</t>
+          <t>B644DU</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>P11佳世達1</t>
+          <t>P15鴻海1A</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>27,100,000</t>
+          <t>99,900,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr"/>
@@ -1917,17 +1917,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>B638BG</t>
+          <t>B644DV</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>P10聯電2</t>
+          <t>P15鴻海1B</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>100,028,603</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr"/>
@@ -1935,17 +1935,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>B638BJ</t>
+          <t>B64613</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>P14聯電1A</t>
+          <t>P10國巨2B</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>250,000,000</t>
+          <t>22,000,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr"/>
@@ -1953,17 +1953,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>B644C6</t>
+          <t>B64614</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>P10鴻海2B</t>
+          <t>P11國巨1</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>160,000,000</t>
+          <t>100,068,351</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr"/>
@@ -1971,17 +1971,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>B644D6</t>
+          <t>B66608</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>P13鴻海1B</t>
+          <t>P10精金2</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>170,000,000</t>
+          <t>14,800,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr"/>
@@ -1989,17 +1989,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>B644DU</t>
+          <t>B67008</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>P15鴻海1A</t>
+          <t>P15東元1</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>99,900,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr"/>
@@ -2007,17 +2007,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>B644DV</t>
+          <t>B68125</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>P15鴻海1B</t>
+          <t>P13南科1</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>100,028,603</t>
+          <t>90,000,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr"/>
@@ -2025,17 +2025,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>B64613</t>
+          <t>B69905</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>P10國巨2B</t>
+          <t>P13環球晶2</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>22,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr"/>
@@ -2043,17 +2043,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>B64614</t>
+          <t>B702AJ</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>P11國巨1</t>
+          <t>P03台化2B</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>100,068,351</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr"/>
@@ -2061,17 +2061,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>B66608</t>
+          <t>B702AT</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>P10精金2</t>
+          <t>P14台化1</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>14,800,000</t>
+          <t>110,170,906</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr"/>
@@ -2079,17 +2079,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>B67008</t>
+          <t>B71310</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>P15東元1</t>
+          <t>P10長春1</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>550,000,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
@@ -2097,17 +2097,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>B68125</t>
+          <t>B718AJ</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>P13南科1</t>
+          <t>P13中油1A</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>90,000,000</t>
+          <t>80,028,604</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -2115,17 +2115,17 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>B69905</t>
+          <t>B718AL</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>P13環球晶2</t>
+          <t>P13中油1C</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -2133,17 +2133,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>B702AP</t>
+          <t>B718AQ</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>P09台化1B</t>
+          <t>P13中油3A</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>170,000,000</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
@@ -2151,17 +2151,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>B702AT</t>
+          <t>B718B3</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>P14台化1</t>
+          <t>P13中油7A</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>110,170,906</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr"/>
@@ -2169,17 +2169,17 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>B71310</t>
+          <t>B718BG</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>P10長春1</t>
+          <t>P14中油4B</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>550,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr"/>
@@ -2187,17 +2187,17 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>B718AJ</t>
+          <t>B72007</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>P13中油1A</t>
+          <t>P10長興1</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>80,028,604</t>
+          <t>465,000,000</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr"/>
@@ -2205,17 +2205,17 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>B718AL</t>
+          <t>B801AU</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>P13中油1C</t>
+          <t>P14中鋼2</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>250,028,603</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr"/>
@@ -2223,17 +2223,17 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>B718AQ</t>
+          <t>B84814</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>P13中油3A</t>
+          <t>P13亞國1</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>170,000,000</t>
+          <t>22,400,000</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr"/>
@@ -2241,17 +2241,17 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>B718B3</t>
+          <t>B84906</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>P13中油7A</t>
+          <t>P11三發1</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>71,400,000</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr"/>
@@ -2259,17 +2259,17 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>B718BG</t>
+          <t>B85413</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>P14中油4B</t>
+          <t>P13中龍2</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>300,113,918</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr"/>
@@ -2277,17 +2277,17 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>B72007</t>
+          <t>B86211</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>P10長興1</t>
+          <t>P12富旺1</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>465,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr"/>
@@ -2295,17 +2295,17 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>B801AU</t>
+          <t>B86909</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>P14中鋼2</t>
+          <t>P12和潤1</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>250,028,603</t>
+          <t>400,000,000</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr"/>
@@ -2313,17 +2313,17 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>B84814</t>
+          <t>B86912</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>P13亞國1</t>
+          <t>P14和潤2A</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>22,400,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr"/>
@@ -2331,17 +2331,17 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>B84906</t>
+          <t>B87003</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>P11三發1</t>
+          <t>P11三圓1</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>71,400,000</t>
+          <t>38,000,000</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr"/>
@@ -2349,17 +2349,17 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>B85413</t>
+          <t>B87109</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>P13中龍2</t>
+          <t>P11日勝2</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>300,113,918</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr"/>
@@ -2367,17 +2367,17 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>B86211</t>
+          <t>B87901</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>P12富旺1</t>
+          <t>P11坤悅1</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>86,285,809</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr"/>
@@ -2385,17 +2385,17 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>B86909</t>
+          <t>B903Z2</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>P12和潤1</t>
+          <t>P12台電3B</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>400,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr"/>
@@ -2403,17 +2403,17 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>B86912</t>
+          <t>B90413</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>P14和潤2A</t>
+          <t>P09元大債2</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>29,100,000</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr"/>
@@ -2421,17 +2421,17 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>B87003</t>
+          <t>B92361</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>P11三圓1</t>
+          <t>P12遠鼎3</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>38,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr"/>
@@ -2439,17 +2439,17 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>B87109</t>
+          <t>B95125</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>P11日勝2</t>
+          <t>P10中租1A</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr"/>
@@ -2457,17 +2457,17 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>B87901</t>
+          <t>B95135</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>P11坤悅1</t>
+          <t>P12中租1A</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>86,285,809</t>
+          <t>147,300,000</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr"/>
@@ -2475,17 +2475,17 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>B903Z2</t>
+          <t>B95148</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>P12台電3B</t>
+          <t>P14中租2A</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>650,000,000</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr"/>
@@ -2493,17 +2493,17 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>B90413</t>
+          <t>B95458</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>P09元大債2</t>
+          <t>P09中控2B</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>29,100,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr"/>
@@ -2511,17 +2511,17 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>B92361</t>
+          <t>B95555</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>P12遠鼎3</t>
+          <t>P09凱控1B</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>561,000,000</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr"/>
@@ -2529,17 +2529,17 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>B95125</t>
+          <t>B95556</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>P10中租1A</t>
+          <t>P09凱控2A</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr"/>
@@ -2547,17 +2547,17 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>B95135</t>
+          <t>B97629</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>P12中租1A</t>
+          <t>P08萬海2B</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>147,300,000</t>
+          <t>98,800,000</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr"/>
@@ -2565,17 +2565,17 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>B95148</t>
+          <t>B97863</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>P14中租2A</t>
+          <t>P11富邦金2</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>650,000,000</t>
+          <t>14,900,000</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr"/>
@@ -2583,17 +2583,17 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>B95458</t>
+          <t>B97867</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>P09中控2B</t>
+          <t>P12富邦金1</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>131,000,000</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr"/>
@@ -2601,17 +2601,17 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>B95555</t>
+          <t>B98008</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>P09凱控1B</t>
+          <t>P11森電1</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>561,000,000</t>
+          <t>90,600,000</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr"/>
@@ -2619,17 +2619,17 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>B95556</t>
+          <t>B98905</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>P09凱控2A</t>
+          <t>P08國泰金1C</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr"/>
@@ -2637,17 +2637,17 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>B97629</t>
+          <t>B98916</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>P08萬海2B</t>
+          <t>P13國泰金2</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>98,800,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr"/>
@@ -2655,17 +2655,17 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>B97863</t>
+          <t>B98919</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>P11富邦金2</t>
+          <t>P14國泰金3</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>14,900,000</t>
+          <t>300,000,000</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr"/>
@@ -2673,17 +2673,17 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>B97867</t>
+          <t>B99209</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>P12富邦金1</t>
+          <t>P14三商2B</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>131,000,000</t>
+          <t>151,400,000</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr"/>
@@ -2691,17 +2691,17 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>B98008</t>
+          <t>B99210</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>P11森電1</t>
+          <t>P14三商3</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>90,600,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr"/>
@@ -2709,17 +2709,17 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>B98905</t>
+          <t>B99503</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>P08國泰金1C</t>
+          <t>P12富壽1A</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr"/>
@@ -2727,17 +2727,17 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>B98916</t>
+          <t>B99509</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>P13國泰金2</t>
+          <t>P13富壽2A</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>30,000,000</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr"/>
@@ -2745,17 +2745,17 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>B98919</t>
+          <t>B99603</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>P14國泰金3</t>
+          <t>P12國壽1A</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>300,000,000</t>
+          <t>62,000,000</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr"/>
@@ -2763,17 +2763,17 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>B99209</t>
+          <t>B99607</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>P14三商2B</t>
+          <t>P13國壽1A</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>151,400,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr"/>
@@ -2781,17 +2781,17 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>B99210</t>
+          <t>B99702</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>P14三商3</t>
+          <t>P12台壽1A</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>14,000,000</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr"/>
@@ -2799,17 +2799,17 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>B99503</t>
+          <t>B99908</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>P12富壽1A</t>
+          <t>P15合迪1A</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>300,000,000</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr"/>
@@ -2817,17 +2817,17 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>B99509</t>
+          <t>B9A506</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>P13富壽2A</t>
+          <t>P09日投控4</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>30,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr"/>
@@ -2835,17 +2835,17 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>B99603</t>
+          <t>B9A508</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>P12國壽1A</t>
+          <t>P15日投控1B</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>62,000,000</t>
+          <t>90,000,000</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr"/>
@@ -2853,17 +2853,17 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>B99607</t>
+          <t>B9AF03</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>P13國壽1A</t>
+          <t>P15光鼎1</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>50,051,458</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr"/>
@@ -2871,17 +2871,17 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>B99702</t>
+          <t>B9AK03</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>P12台壽1A</t>
+          <t>P13凱基壽1A</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>14,000,000</t>
+          <t>152,000,000</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr"/>
@@ -2889,17 +2889,17 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>B99908</t>
+          <t>B9AS01</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>P15合迪1A</t>
+          <t>P11北基1</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>300,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr"/>
@@ -2907,17 +2907,17 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>B9A506</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>P09日投控4</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>5,323,934,247</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr"/>
@@ -2925,17 +2925,17 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>B9A508</t>
+          <t>G10323</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>P15日投控1B</t>
+          <t>P14高銀2</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>90,000,000</t>
+          <t>30,000,000</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr"/>
@@ -2943,17 +2943,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>B9AF03</t>
+          <t>G10924</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>P15光鼎1</t>
+          <t>P14聯邦1</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>50,051,458</t>
+          <t>200,112,439</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr"/>
@@ -2961,17 +2961,17 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>B9AK03</t>
+          <t>G11663</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>P13凱基壽1A</t>
+          <t>P13新光銀1</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>152,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr"/>
@@ -2979,17 +2979,17 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>B9AS01</t>
+          <t>G11748</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>P11北基1</t>
+          <t>P15王道銀1A</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr"/>
@@ -2997,17 +2997,17 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>G12728</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>P10土銀2A</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>4,040,973,484</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr"/>
@@ -3015,17 +3015,17 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>G10323</t>
+          <t>G13710</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>P14高銀2</t>
+          <t>P08法興2C</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>30,000,000</t>
+          <t>270,000,000</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr"/>
@@ -3033,17 +3033,17 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>G10924</t>
+          <t>G14012</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>P14聯邦1</t>
+          <t>P15匯理3</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>200,112,439</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr"/>
@@ -3051,17 +3051,17 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>G11663</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>P13新光銀1</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>1,875,180,490</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
@@ -3069,17 +3069,17 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>G11748</t>
+          <t>PFUR_NTD</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>P15王道銀1A</t>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>-146,774,750</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr"/>
@@ -3087,110 +3087,20 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>G12728</t>
+          <t>RDI_NTD</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>P10土銀2A</t>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>148,827,517</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>G13710</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>P08法興2C</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>270,000,000</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>G14012</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>P15匯理3</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>200,000,000</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>M_NTD</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>MARGIN</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>1,761,944,890</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>PFUR_NTD</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>-146,774,750</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>742,971,076</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
